--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/34.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/34.xlsx
@@ -426,13 +426,13 @@
         <v>-9.898098813655679</v>
       </c>
       <c r="E2">
-        <v>-10.48665726337996</v>
+        <v>-9.680480206638457</v>
       </c>
       <c r="F2">
-        <v>-6.118909096813241</v>
+        <v>-5.585251621642521</v>
       </c>
       <c r="G2">
-        <v>-4.400633193474119</v>
+        <v>-3.677815301520727</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.737184288477252</v>
       </c>
       <c r="E3">
-        <v>-9.590395273203869</v>
+        <v>-10.6045198563776</v>
       </c>
       <c r="F3">
-        <v>-5.800258522876147</v>
+        <v>-5.672106772193452</v>
       </c>
       <c r="G3">
-        <v>-4.131638126226179</v>
+        <v>-3.606151922232124</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.416953541812944</v>
       </c>
       <c r="E4">
-        <v>-10.71321681798371</v>
+        <v>-11.09200555482931</v>
       </c>
       <c r="F4">
-        <v>-6.516128662171063</v>
+        <v>-5.497115815086862</v>
       </c>
       <c r="G4">
-        <v>-4.109013858010799</v>
+        <v>-3.504005039617911</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.952876560536685</v>
       </c>
       <c r="E5">
-        <v>-11.18339016030409</v>
+        <v>-11.46779191340782</v>
       </c>
       <c r="F5">
-        <v>-6.292821933745087</v>
+        <v>-5.836037367737863</v>
       </c>
       <c r="G5">
-        <v>-3.425909270346504</v>
+        <v>-2.999401756885579</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.355444841773936</v>
       </c>
       <c r="E6">
-        <v>-12.94666019856673</v>
+        <v>-12.27528222761155</v>
       </c>
       <c r="F6">
-        <v>-5.790318942409955</v>
+        <v>-5.290932683427857</v>
       </c>
       <c r="G6">
-        <v>-3.960671622941597</v>
+        <v>-2.401361636852857</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.653417072601314</v>
       </c>
       <c r="E7">
-        <v>-12.56160405369452</v>
+        <v>-12.77869909762224</v>
       </c>
       <c r="F7">
-        <v>-6.053032350738207</v>
+        <v>-5.507009006978497</v>
       </c>
       <c r="G7">
-        <v>-3.599285850783675</v>
+        <v>-3.404516525071734</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.867601193388493</v>
       </c>
       <c r="E8">
-        <v>-13.87251123790894</v>
+        <v>-13.10760216479934</v>
       </c>
       <c r="F8">
-        <v>-6.313987963437719</v>
+        <v>-5.895853777894016</v>
       </c>
       <c r="G8">
-        <v>-3.473389114470731</v>
+        <v>-2.689041423124445</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.01511047817668</v>
       </c>
       <c r="E9">
-        <v>-14.1192677865869</v>
+        <v>-14.31871083883272</v>
       </c>
       <c r="F9">
-        <v>-6.053330563003215</v>
+        <v>-5.682394266968819</v>
       </c>
       <c r="G9">
-        <v>-2.828713339426296</v>
+        <v>-2.221999590080683</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.117213946460621</v>
       </c>
       <c r="E10">
-        <v>-14.74679201525181</v>
+        <v>-12.94920972943305</v>
       </c>
       <c r="F10">
-        <v>-5.923927977542293</v>
+        <v>-5.434367812692202</v>
       </c>
       <c r="G10">
-        <v>-2.549253637728719</v>
+        <v>-1.877623400903538</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.200552349020428</v>
       </c>
       <c r="E11">
-        <v>-14.85151297667918</v>
+        <v>-15.27278785666474</v>
       </c>
       <c r="F11">
-        <v>-5.849911693367352</v>
+        <v>-5.55602847640656</v>
       </c>
       <c r="G11">
-        <v>-1.698503023955731</v>
+        <v>-2.022247893332139</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.288559177741464</v>
       </c>
       <c r="E12">
-        <v>-15.28389620340556</v>
+        <v>-15.83056905713751</v>
       </c>
       <c r="F12">
-        <v>-5.564724677401149</v>
+        <v>-5.207060483894407</v>
       </c>
       <c r="G12">
-        <v>-0.8963810136090968</v>
+        <v>-1.370616662109694</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.405391946649394</v>
       </c>
       <c r="E13">
-        <v>-16.63948131217965</v>
+        <v>-17.26410731747965</v>
       </c>
       <c r="F13">
-        <v>-5.843444629053696</v>
+        <v>-4.995089549192041</v>
       </c>
       <c r="G13">
-        <v>-1.493067120516257</v>
+        <v>-0.5390672124644791</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.590760217516119</v>
       </c>
       <c r="E14">
-        <v>-17.30749009847313</v>
+        <v>-18.55710438699374</v>
       </c>
       <c r="F14">
-        <v>-5.191309077730175</v>
+        <v>-4.618753954426198</v>
       </c>
       <c r="G14">
-        <v>-1.017275515612202</v>
+        <v>-0.1516804156411219</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.8744883022221085</v>
       </c>
       <c r="E15">
-        <v>-19.15505315191455</v>
+        <v>-18.28399211959114</v>
       </c>
       <c r="F15">
-        <v>-4.639714134819234</v>
+        <v>-4.527887020543509</v>
       </c>
       <c r="G15">
-        <v>-0.3720832954636404</v>
+        <v>0.1142093598909828</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.2785432586305635</v>
       </c>
       <c r="E16">
-        <v>-19.43978095514682</v>
+        <v>-19.43372638539856</v>
       </c>
       <c r="F16">
-        <v>-5.020154290065949</v>
+        <v>-4.505453174540893</v>
       </c>
       <c r="G16">
-        <v>0.0505177742609444</v>
+        <v>0.213545589342354</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.1771935233891502</v>
       </c>
       <c r="E17">
-        <v>-20.34473761541764</v>
+        <v>-21.44902411608409</v>
       </c>
       <c r="F17">
-        <v>-4.783486409616519</v>
+        <v>-3.888617671720269</v>
       </c>
       <c r="G17">
-        <v>0.9094950936990215</v>
+        <v>0.8265096486661107</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.4896688316993568</v>
       </c>
       <c r="E18">
-        <v>-21.64268883549612</v>
+        <v>-21.71046650596892</v>
       </c>
       <c r="F18">
-        <v>-3.789339495229554</v>
+        <v>-3.744110635036701</v>
       </c>
       <c r="G18">
-        <v>1.353075090505968</v>
+        <v>1.059601849540656</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.673093060147779</v>
       </c>
       <c r="E19">
-        <v>-22.83285784571803</v>
+        <v>-22.36381209342556</v>
       </c>
       <c r="F19">
-        <v>-3.788660233959258</v>
+        <v>-3.421928730861472</v>
       </c>
       <c r="G19">
-        <v>0.8832457781181402</v>
+        <v>1.256145627661647</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7493774971586089</v>
       </c>
       <c r="E20">
-        <v>-23.10554896503792</v>
+        <v>-23.19682035866252</v>
       </c>
       <c r="F20">
-        <v>-3.811859491442061</v>
+        <v>-3.296074871354143</v>
       </c>
       <c r="G20">
-        <v>0.827674960695934</v>
+        <v>1.497050716008872</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.7456488663761076</v>
       </c>
       <c r="E21">
-        <v>-24.06307215158978</v>
+        <v>-23.96618545019567</v>
       </c>
       <c r="F21">
-        <v>-3.110016925746152</v>
+        <v>-2.89107279424702</v>
       </c>
       <c r="G21">
-        <v>1.22192782896774</v>
+        <v>1.811410188781446</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.6958429302232029</v>
       </c>
       <c r="E22">
-        <v>-25.17918702636426</v>
+        <v>-25.30622883617545</v>
       </c>
       <c r="F22">
-        <v>-3.089736834990815</v>
+        <v>-2.788901130418326</v>
       </c>
       <c r="G22">
-        <v>1.384055175662468</v>
+        <v>1.463597653334537</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.632467818885411</v>
       </c>
       <c r="E23">
-        <v>-25.15279507984756</v>
+        <v>-25.50883729175263</v>
       </c>
       <c r="F23">
-        <v>-2.645723623416251</v>
+        <v>-2.594593473845855</v>
       </c>
       <c r="G23">
-        <v>1.07879639257735</v>
+        <v>1.5028276179749</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.5821401128791469</v>
       </c>
       <c r="E24">
-        <v>-27.23449835338156</v>
+        <v>-26.72216491804977</v>
       </c>
       <c r="F24">
-        <v>-2.937738871883731</v>
+        <v>-2.199264242901222</v>
       </c>
       <c r="G24">
-        <v>-0.5609333657513653</v>
+        <v>1.4011706961005</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.5707214969626224</v>
       </c>
       <c r="E25">
-        <v>-26.95484244103788</v>
+        <v>-26.46533251470474</v>
       </c>
       <c r="F25">
-        <v>-2.538151832488708</v>
+        <v>-2.197614963402248</v>
       </c>
       <c r="G25">
-        <v>0.9498638860048944</v>
+        <v>1.242582322587253</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.6168312710428759</v>
       </c>
       <c r="E26">
-        <v>-28.04584239896582</v>
+        <v>-26.59133730396817</v>
       </c>
       <c r="F26">
-        <v>-2.0675240046296</v>
+        <v>-1.773793207270923</v>
       </c>
       <c r="G26">
-        <v>0.4642134764848898</v>
+        <v>0.6799815925524286</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.7303651185500781</v>
       </c>
       <c r="E27">
-        <v>-27.85186068637325</v>
+        <v>-26.99626892126005</v>
       </c>
       <c r="F27">
-        <v>-2.584760752774625</v>
+        <v>-1.882507316846927</v>
       </c>
       <c r="G27">
-        <v>-0.7940123244437532</v>
+        <v>1.370428970222827</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.9187345093706405</v>
       </c>
       <c r="E28">
-        <v>-27.83876433954307</v>
+        <v>-27.39291795959189</v>
       </c>
       <c r="F28">
-        <v>-2.091165610305497</v>
+        <v>-2.054624667433206</v>
       </c>
       <c r="G28">
-        <v>0.1974629591125746</v>
+        <v>1.599419405174215</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.181606919581107</v>
       </c>
       <c r="E29">
-        <v>-27.2443206135042</v>
+        <v>-27.95014668623573</v>
       </c>
       <c r="F29">
-        <v>-2.151735834798197</v>
+        <v>-1.731095837861025</v>
       </c>
       <c r="G29">
-        <v>-1.174384075269395</v>
+        <v>0.02313625210563241</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.507829839620189</v>
       </c>
       <c r="E30">
-        <v>-26.82087659446897</v>
+        <v>-26.90556358688641</v>
       </c>
       <c r="F30">
-        <v>-2.083305232020333</v>
+        <v>-1.766494462084856</v>
       </c>
       <c r="G30">
-        <v>-0.362482713399754</v>
+        <v>1.318142213975578</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.88826627879739</v>
       </c>
       <c r="E31">
-        <v>-27.15335715611212</v>
+        <v>-27.15790374401583</v>
       </c>
       <c r="F31">
-        <v>-2.629659094373761</v>
+        <v>-2.113181959137103</v>
       </c>
       <c r="G31">
-        <v>-0.1758738824421157</v>
+        <v>0.2380038997864895</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.308160204404358</v>
       </c>
       <c r="E32">
-        <v>-26.45451851877443</v>
+        <v>-26.73238115541107</v>
       </c>
       <c r="F32">
-        <v>-2.492543580025373</v>
+        <v>-2.033712532349532</v>
       </c>
       <c r="G32">
-        <v>-0.8483648611075075</v>
+        <v>0.5748188029519401</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.747303422559005</v>
       </c>
       <c r="E33">
-        <v>-25.68102798742028</v>
+        <v>-26.68741340851491</v>
       </c>
       <c r="F33">
-        <v>-2.223846045579297</v>
+        <v>-1.982400970317922</v>
       </c>
       <c r="G33">
-        <v>-0.1402391702574007</v>
+        <v>0.6317370124086297</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.186963827035117</v>
       </c>
       <c r="E34">
-        <v>-24.90760991165026</v>
+        <v>-26.09734418836744</v>
       </c>
       <c r="F34">
-        <v>-2.19255860877556</v>
+        <v>-2.182585065245854</v>
       </c>
       <c r="G34">
-        <v>-0.7344887156476573</v>
+        <v>0.8085863551164965</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.61177802262323</v>
       </c>
       <c r="E35">
-        <v>-25.27638166399089</v>
+        <v>-25.51155437615723</v>
       </c>
       <c r="F35">
-        <v>-2.49421771054643</v>
+        <v>-2.177452500818108</v>
       </c>
       <c r="G35">
-        <v>-1.144840766876939</v>
+        <v>0.06677255285876593</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.006058554752197</v>
       </c>
       <c r="E36">
-        <v>-23.89042860852135</v>
+        <v>-24.71115565224951</v>
       </c>
       <c r="F36">
-        <v>-2.748656556888118</v>
+        <v>-2.367301884028712</v>
       </c>
       <c r="G36">
-        <v>-1.097357612207172</v>
+        <v>1.10468816923999</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.354892694860082</v>
       </c>
       <c r="E37">
-        <v>-23.34496032887544</v>
+        <v>-23.31842347119049</v>
       </c>
       <c r="F37">
-        <v>-2.441894711916003</v>
+        <v>-2.435405281682471</v>
       </c>
       <c r="G37">
-        <v>-1.021618951359726</v>
+        <v>-0.1804887829238598</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.652916334158129</v>
       </c>
       <c r="E38">
-        <v>-22.76193741428391</v>
+        <v>-23.96711831584125</v>
       </c>
       <c r="F38">
-        <v>-2.585324870975931</v>
+        <v>-2.478571507042353</v>
       </c>
       <c r="G38">
-        <v>-0.5742318271826177</v>
+        <v>-0.2104326673265677</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.896063936157049</v>
       </c>
       <c r="E39">
-        <v>-21.99422521576355</v>
+        <v>-22.59803382605029</v>
       </c>
       <c r="F39">
-        <v>-3.025813379251582</v>
+        <v>-2.560330541331262</v>
       </c>
       <c r="G39">
-        <v>-0.7825313525135608</v>
+        <v>0.4664580263605156</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.079074553158411</v>
       </c>
       <c r="E40">
-        <v>-23.22263266050624</v>
+        <v>-22.1201801918129</v>
       </c>
       <c r="F40">
-        <v>-2.721563972612158</v>
+        <v>-2.437123315675877</v>
       </c>
       <c r="G40">
-        <v>-1.16141335784653</v>
+        <v>-0.3548320426584983</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.205723215100554</v>
       </c>
       <c r="E41">
-        <v>-21.40218158094875</v>
+        <v>-21.50061702045348</v>
       </c>
       <c r="F41">
-        <v>-2.87426273454201</v>
+        <v>-2.169258290469615</v>
       </c>
       <c r="G41">
-        <v>-0.7367862342519115</v>
+        <v>-0.4507021309302526</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.280620190703761</v>
       </c>
       <c r="E42">
-        <v>-19.77698471517998</v>
+        <v>-20.59966353120544</v>
       </c>
       <c r="F42">
-        <v>-2.823125958032391</v>
+        <v>-2.449912480007699</v>
       </c>
       <c r="G42">
-        <v>-0.4989500216195908</v>
+        <v>0.5921428877589462</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.306135053164787</v>
       </c>
       <c r="E43">
-        <v>-19.27954995933342</v>
+        <v>-21.5731269462643</v>
       </c>
       <c r="F43">
-        <v>-2.59973183684542</v>
+        <v>-2.789478502498078</v>
       </c>
       <c r="G43">
-        <v>-1.590662003013972</v>
+        <v>0.04653187743166189</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.287751833144748</v>
       </c>
       <c r="E44">
-        <v>-19.32453129165161</v>
+        <v>-19.6036619010104</v>
       </c>
       <c r="F44">
-        <v>-2.576594706917827</v>
+        <v>-2.472571641943877</v>
       </c>
       <c r="G44">
-        <v>-0.3453870562349576</v>
+        <v>0.587647166916616</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.232950616085354</v>
       </c>
       <c r="E45">
-        <v>-19.47173839621895</v>
+        <v>-19.023075305435</v>
       </c>
       <c r="F45">
-        <v>-2.303718887292031</v>
+        <v>-2.245043139049534</v>
       </c>
       <c r="G45">
-        <v>-0.331426485695851</v>
+        <v>0.2034682887208125</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.145533918713537</v>
       </c>
       <c r="E46">
-        <v>-18.47969012383261</v>
+        <v>-18.34553408135538</v>
       </c>
       <c r="F46">
-        <v>-2.399316627412108</v>
+        <v>-2.47444872247862</v>
       </c>
       <c r="G46">
-        <v>-0.5740662999056541</v>
+        <v>0.2593403657870924</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.02753745897418</v>
       </c>
       <c r="E47">
-        <v>-16.58836842605508</v>
+        <v>-17.5595676041101</v>
       </c>
       <c r="F47">
-        <v>-2.881670824225246</v>
+        <v>-2.250274279198212</v>
       </c>
       <c r="G47">
-        <v>-1.010793467446309</v>
+        <v>0.5856807028662889</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.885826312081894</v>
       </c>
       <c r="E48">
-        <v>-17.09933879071056</v>
+        <v>-18.10703746926741</v>
       </c>
       <c r="F48">
-        <v>-2.830775930997244</v>
+        <v>-2.231793402441755</v>
       </c>
       <c r="G48">
-        <v>-0.03762219017661168</v>
+        <v>0.8327732008264117</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.721975516069641</v>
       </c>
       <c r="E49">
-        <v>-16.36040504450895</v>
+        <v>-16.01927056903714</v>
       </c>
       <c r="F49">
-        <v>-2.2912229650208</v>
+        <v>-2.261493687301729</v>
       </c>
       <c r="G49">
-        <v>-0.5854876820161397</v>
+        <v>0.4922008284738884</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.532868199345048</v>
       </c>
       <c r="E50">
-        <v>-14.77946948369116</v>
+        <v>-16.74797902092943</v>
       </c>
       <c r="F50">
-        <v>-2.332871621298754</v>
+        <v>-2.329243372074492</v>
       </c>
       <c r="G50">
-        <v>-0.2568266525139141</v>
+        <v>0.3468612582088047</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.322611430049951</v>
       </c>
       <c r="E51">
-        <v>-15.02954540381674</v>
+        <v>-15.01315232790897</v>
       </c>
       <c r="F51">
-        <v>-3.093359285643257</v>
+        <v>-2.560657746455368</v>
       </c>
       <c r="G51">
-        <v>0.1802547433994429</v>
+        <v>1.646882696570746</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.090278335097112</v>
       </c>
       <c r="E52">
-        <v>-15.33228294817751</v>
+        <v>-14.06921909185413</v>
       </c>
       <c r="F52">
-        <v>-2.269268743744405</v>
+        <v>-2.092130658329759</v>
       </c>
       <c r="G52">
-        <v>0.01241008455839377</v>
+        <v>0.3896633014860419</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.832313587433297</v>
       </c>
       <c r="E53">
-        <v>-13.88230632718754</v>
+        <v>-13.50667393672529</v>
       </c>
       <c r="F53">
-        <v>-2.630122151751926</v>
+        <v>-2.6055254384606</v>
       </c>
       <c r="G53">
-        <v>-0.8685658099881404</v>
+        <v>0.9418622974364759</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.549903582263883</v>
       </c>
       <c r="E54">
-        <v>-12.54871148819468</v>
+        <v>-13.82733518120842</v>
       </c>
       <c r="F54">
-        <v>-2.394101226244082</v>
+        <v>-2.220558255357586</v>
       </c>
       <c r="G54">
-        <v>-0.266470271669811</v>
+        <v>-0.0744222143911502</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.244114160420507</v>
       </c>
       <c r="E55">
-        <v>-13.25737238565502</v>
+        <v>-12.84954254499823</v>
       </c>
       <c r="F55">
-        <v>-2.521402243604102</v>
+        <v>-2.400464744632388</v>
       </c>
       <c r="G55">
-        <v>-0.3950915869615752</v>
+        <v>0.4957033856544373</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.913910071418897</v>
       </c>
       <c r="E56">
-        <v>-12.62899680387667</v>
+        <v>-11.81176574208244</v>
       </c>
       <c r="F56">
-        <v>-3.16485816128109</v>
+        <v>-2.427236750723465</v>
       </c>
       <c r="G56">
-        <v>-0.3883976638811689</v>
+        <v>0.6578208007125473</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.560981065137518</v>
       </c>
       <c r="E57">
-        <v>-12.02919136461272</v>
+        <v>-12.07113861934577</v>
       </c>
       <c r="F57">
-        <v>-2.881773541783193</v>
+        <v>-2.31191806784494</v>
       </c>
       <c r="G57">
-        <v>-0.5712390940151165</v>
+        <v>-0.05034130613849158</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.192150888256312</v>
       </c>
       <c r="E58">
-        <v>-10.33446883740419</v>
+        <v>-10.62816301917165</v>
       </c>
       <c r="F58">
-        <v>-2.970796529827251</v>
+        <v>-2.416519333266045</v>
       </c>
       <c r="G58">
-        <v>-0.2444981809256682</v>
+        <v>0.4339617113470297</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.812416581942921</v>
       </c>
       <c r="E59">
-        <v>-10.45003096560593</v>
+        <v>-10.92352820784794</v>
       </c>
       <c r="F59">
-        <v>-2.647133504735816</v>
+        <v>-2.113080069946558</v>
       </c>
       <c r="G59">
-        <v>0.4799551205241243</v>
+        <v>0.02199411389458385</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.427616116087979</v>
       </c>
       <c r="E60">
-        <v>-10.60743619363854</v>
+        <v>-9.867963559030017</v>
       </c>
       <c r="F60">
-        <v>-3.033679556108567</v>
+        <v>-2.368719220654902</v>
       </c>
       <c r="G60">
-        <v>0.2675571398155634</v>
+        <v>-0.09839056409547359</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.050693982208531</v>
       </c>
       <c r="E61">
-        <v>-11.9751576127532</v>
+        <v>-8.990585305465908</v>
       </c>
       <c r="F61">
-        <v>-2.812444160373291</v>
+        <v>-2.208117833702343</v>
       </c>
       <c r="G61">
-        <v>-1.273481945441939</v>
+        <v>-0.4395786979183014</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.6922873907051087</v>
       </c>
       <c r="E62">
-        <v>-9.85030703887411</v>
+        <v>-9.021732149690665</v>
       </c>
       <c r="F62">
-        <v>-3.080865020106832</v>
+        <v>-2.556467035764605</v>
       </c>
       <c r="G62">
-        <v>-1.596554774073874</v>
+        <v>-0.7512864237139193</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.3622532943528683</v>
       </c>
       <c r="E63">
-        <v>-10.04278529809613</v>
+        <v>-8.41298750273557</v>
       </c>
       <c r="F63">
-        <v>-2.92339072009984</v>
+        <v>-2.498542616756446</v>
       </c>
       <c r="G63">
-        <v>-1.666840966418141</v>
+        <v>-0.7058028385498725</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.0729041661748203</v>
       </c>
       <c r="E64">
-        <v>-9.809999091731836</v>
+        <v>-8.831164906499881</v>
       </c>
       <c r="F64">
-        <v>-3.320905184253058</v>
+        <v>-2.72238736981054</v>
       </c>
       <c r="G64">
-        <v>-1.514191711602346</v>
+        <v>-0.5136289805407193</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.1645582060942141</v>
       </c>
       <c r="E65">
-        <v>-9.444012350905926</v>
+        <v>-8.570936147649103</v>
       </c>
       <c r="F65">
-        <v>-2.758662406746534</v>
+        <v>-2.582852194278574</v>
       </c>
       <c r="G65">
-        <v>-1.124186273257426</v>
+        <v>-1.379671004159601</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.3426458607599575</v>
       </c>
       <c r="E66">
-        <v>-7.81719429144241</v>
+        <v>-8.637454902347773</v>
       </c>
       <c r="F66">
-        <v>-2.86261340375644</v>
+        <v>-2.709256918108765</v>
       </c>
       <c r="G66">
-        <v>-1.734958751434185</v>
+        <v>-0.929916839921914</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.4571220019738012</v>
       </c>
       <c r="E67">
-        <v>-7.55508621587845</v>
+        <v>-7.952808502550115</v>
       </c>
       <c r="F67">
-        <v>-2.974685714783394</v>
+        <v>-2.419196616711893</v>
       </c>
       <c r="G67">
-        <v>-1.830130314597153</v>
+        <v>-1.231858456376682</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.5027232455307761</v>
       </c>
       <c r="E68">
-        <v>-8.524098140987769</v>
+        <v>-7.627532743053161</v>
       </c>
       <c r="F68">
-        <v>-2.817663703378331</v>
+        <v>-2.640733538181787</v>
       </c>
       <c r="G68">
-        <v>-2.135054732582804</v>
+        <v>-1.105130773133381</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.4802410033236037</v>
       </c>
       <c r="E69">
-        <v>-9.660989654509443</v>
+        <v>-7.349638407098461</v>
       </c>
       <c r="F69">
-        <v>-3.052514974113421</v>
+        <v>-2.706199414025032</v>
       </c>
       <c r="G69">
-        <v>-2.499115425536456</v>
+        <v>-1.498320956287081</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.3953568139000976</v>
       </c>
       <c r="E70">
-        <v>-8.652013946282434</v>
+        <v>-7.172919237423134</v>
       </c>
       <c r="F70">
-        <v>-2.981513118917268</v>
+        <v>-2.407830587578081</v>
       </c>
       <c r="G70">
-        <v>-2.205039665282997</v>
+        <v>-1.211028503843588</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.2545581133617617</v>
       </c>
       <c r="E71">
-        <v>-7.195634063045608</v>
+        <v>-7.1861242676295</v>
       </c>
       <c r="F71">
-        <v>-3.070995850869878</v>
+        <v>-2.890149992960302</v>
       </c>
       <c r="G71">
-        <v>-1.564214054700734</v>
+        <v>-1.735448712173997</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.06608144068023156</v>
       </c>
       <c r="E72">
-        <v>-8.238048023345256</v>
+        <v>-7.683060891335215</v>
       </c>
       <c r="F72">
-        <v>-2.648929405265086</v>
+        <v>-2.53177588858936</v>
       </c>
       <c r="G72">
-        <v>-1.611697209370501</v>
+        <v>-0.6216322182139025</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.1596910362148322</v>
       </c>
       <c r="E73">
-        <v>-8.198817853016807</v>
+        <v>-7.853766247528356</v>
       </c>
       <c r="F73">
-        <v>-3.226023981936403</v>
+        <v>-2.889172519424998</v>
       </c>
       <c r="G73">
-        <v>-1.489746643340368</v>
+        <v>-1.513999699961069</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.4111037283626033</v>
       </c>
       <c r="E74">
-        <v>-8.935437549000499</v>
+        <v>-7.834977608870532</v>
       </c>
       <c r="F74">
-        <v>-3.33206080806656</v>
+        <v>-2.568728530060843</v>
       </c>
       <c r="G74">
-        <v>-2.41983779150753</v>
+        <v>-1.584017738116654</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.6808605890953906</v>
       </c>
       <c r="E75">
-        <v>-9.146967098372789</v>
+        <v>-8.045492780065103</v>
       </c>
       <c r="F75">
-        <v>-3.391440668601437</v>
+        <v>-2.900298322011998</v>
       </c>
       <c r="G75">
-        <v>-1.062173134215798</v>
+        <v>-0.8545820656302588</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.9624066380081749</v>
       </c>
       <c r="E76">
-        <v>-10.89033449337171</v>
+        <v>-7.699136974062444</v>
       </c>
       <c r="F76">
-        <v>-3.255724266796377</v>
+        <v>-2.758026220581183</v>
       </c>
       <c r="G76">
-        <v>-1.323414903810766</v>
+        <v>-1.413501469025413</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.248395477976716</v>
       </c>
       <c r="E77">
-        <v>-10.12145847703139</v>
+        <v>-8.861741162999671</v>
       </c>
       <c r="F77">
-        <v>-3.728035337217974</v>
+        <v>-3.156389761322271</v>
       </c>
       <c r="G77">
-        <v>-1.429567546527496</v>
+        <v>-1.17731390807165</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.536932125042781</v>
       </c>
       <c r="E78">
-        <v>-10.16401254728147</v>
+        <v>-9.756762351297663</v>
       </c>
       <c r="F78">
-        <v>-3.115904132877848</v>
+        <v>-2.797077945051361</v>
       </c>
       <c r="G78">
-        <v>-0.4378836986021946</v>
+        <v>-0.4716380209206036</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.828851638942181</v>
       </c>
       <c r="E79">
-        <v>-10.77763436074282</v>
+        <v>-10.2150393923999</v>
       </c>
       <c r="F79">
-        <v>-3.271709272568199</v>
+        <v>-3.181298769124452</v>
       </c>
       <c r="G79">
-        <v>-1.248550226985687</v>
+        <v>-0.9549611169265005</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.124105506061652</v>
       </c>
       <c r="E80">
-        <v>-11.08514944518169</v>
+        <v>-9.978019062838429</v>
       </c>
       <c r="F80">
-        <v>-3.760546272675646</v>
+        <v>-3.237039611658831</v>
       </c>
       <c r="G80">
-        <v>-1.186517224670824</v>
+        <v>-0.9577783911804203</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.422371981679243</v>
       </c>
       <c r="E81">
-        <v>-13.1438299568607</v>
+        <v>-11.47340722117733</v>
       </c>
       <c r="F81">
-        <v>-3.438791806080262</v>
+        <v>-3.266358847513517</v>
       </c>
       <c r="G81">
-        <v>-1.22986881850758</v>
+        <v>-0.87465390323486</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.726527899837285</v>
       </c>
       <c r="E82">
-        <v>-13.62235380525123</v>
+        <v>-12.0933553128274</v>
       </c>
       <c r="F82">
-        <v>-3.490254130979181</v>
+        <v>-3.214124484195188</v>
       </c>
       <c r="G82">
-        <v>-0.6535260139392411</v>
+        <v>0.393791551773513</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.035876546586104</v>
       </c>
       <c r="E83">
-        <v>-14.97122771554596</v>
+        <v>-13.60034089309994</v>
       </c>
       <c r="F83">
-        <v>-3.474109250298619</v>
+        <v>-3.191116579582432</v>
       </c>
       <c r="G83">
-        <v>-0.1045680420717536</v>
+        <v>0.4160516599795725</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.343929842718737</v>
       </c>
       <c r="E84">
-        <v>-14.38695947060232</v>
+        <v>-14.21625411440918</v>
       </c>
       <c r="F84">
-        <v>-4.345418390891848</v>
+        <v>-3.853407915264276</v>
       </c>
       <c r="G84">
-        <v>0.01501217335226092</v>
+        <v>0.4744695465655519</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.647383406875476</v>
       </c>
       <c r="E85">
-        <v>-16.70585515571008</v>
+        <v>-15.60860590365155</v>
       </c>
       <c r="F85">
-        <v>-3.399199157696057</v>
+        <v>-3.477010192943223</v>
       </c>
       <c r="G85">
-        <v>-0.7055744109076627</v>
+        <v>0.8044216888280933</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.937522937405519</v>
       </c>
       <c r="E86">
-        <v>-17.33371449145155</v>
+        <v>-17.17315291703559</v>
       </c>
       <c r="F86">
-        <v>-3.822284495206293</v>
+        <v>-3.265634026036067</v>
       </c>
       <c r="G86">
-        <v>-0.354365255737461</v>
+        <v>0.8376099078592869</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.199375801549376</v>
       </c>
       <c r="E87">
-        <v>-18.90222844806631</v>
+        <v>-18.06305240123091</v>
       </c>
       <c r="F87">
-        <v>-4.007612649132418</v>
+        <v>-3.181936612024608</v>
       </c>
       <c r="G87">
-        <v>0.4172500774647887</v>
+        <v>0.444293923975095</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.418612749829829</v>
       </c>
       <c r="E88">
-        <v>-21.15459179305338</v>
+        <v>-19.8066960331443</v>
       </c>
       <c r="F88">
-        <v>-3.948018241440216</v>
+        <v>-3.69498844805069</v>
       </c>
       <c r="G88">
-        <v>-0.1311384805699442</v>
+        <v>1.40293852741847</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.579115122498401</v>
       </c>
       <c r="E89">
-        <v>-22.11329238284723</v>
+        <v>-21.53147857081575</v>
       </c>
       <c r="F89">
-        <v>-4.144902120635394</v>
+        <v>-3.5434916472223</v>
       </c>
       <c r="G89">
-        <v>0.04292669333939557</v>
+        <v>1.314629725158412</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.663384068127205</v>
       </c>
       <c r="E90">
-        <v>-23.90443970710109</v>
+        <v>-22.91563835057825</v>
       </c>
       <c r="F90">
-        <v>-4.119814185474208</v>
+        <v>-3.646229914354508</v>
       </c>
       <c r="G90">
-        <v>-1.307974519415605</v>
+        <v>1.411860447646806</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.658115035685569</v>
       </c>
       <c r="E91">
-        <v>-25.89815925914006</v>
+        <v>-24.87469696256251</v>
       </c>
       <c r="F91">
-        <v>-3.95797356088706</v>
+        <v>-3.622242879471643</v>
       </c>
       <c r="G91">
-        <v>-0.2217315592521002</v>
+        <v>0.7343539924894186</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.555224336225534</v>
       </c>
       <c r="E92">
-        <v>-27.74631101420247</v>
+        <v>-27.12959172451987</v>
       </c>
       <c r="F92">
-        <v>-4.093443109206086</v>
+        <v>-3.769086740598509</v>
       </c>
       <c r="G92">
-        <v>-0.4844200372477296</v>
+        <v>0.7778678030575991</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.350128851376727</v>
       </c>
       <c r="E93">
-        <v>-29.86719011637683</v>
+        <v>-30.13178885264501</v>
       </c>
       <c r="F93">
-        <v>-3.896183151210037</v>
+        <v>-3.494394311258373</v>
       </c>
       <c r="G93">
-        <v>-0.4921005028988388</v>
+        <v>0.5744248480327668</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.043950568771329</v>
       </c>
       <c r="E94">
-        <v>-33.43130067750674</v>
+        <v>-32.37494807421149</v>
       </c>
       <c r="F94">
-        <v>-4.670713299766797</v>
+        <v>-3.638679345477991</v>
       </c>
       <c r="G94">
-        <v>-0.1763704642730064</v>
+        <v>0.6169322527570089</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.647446808194376</v>
       </c>
       <c r="E95">
-        <v>-35.23824784757336</v>
+        <v>-33.65289023188707</v>
       </c>
       <c r="F95">
-        <v>-3.972754120455212</v>
+        <v>-4.088318000084965</v>
       </c>
       <c r="G95">
-        <v>-0.6599517828309666</v>
+        <v>0.7455204625933803</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.170137262905997</v>
       </c>
       <c r="E96">
-        <v>-37.22711513971312</v>
+        <v>-37.00239867403049</v>
       </c>
       <c r="F96">
-        <v>-4.309643687867146</v>
+        <v>-4.015765441110771</v>
       </c>
       <c r="G96">
-        <v>-1.382577663143081</v>
+        <v>-0.3062034392321438</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.634032382609172</v>
       </c>
       <c r="E97">
-        <v>-39.60515948807206</v>
+        <v>-39.12143468728373</v>
       </c>
       <c r="F97">
-        <v>-4.855411894466794</v>
+        <v>-4.119901992418905</v>
       </c>
       <c r="G97">
-        <v>-1.959526297545107</v>
+        <v>-0.4140742550837562</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.054312329299679</v>
       </c>
       <c r="E98">
-        <v>-41.9527294705964</v>
+        <v>-41.68187691172362</v>
       </c>
       <c r="F98">
-        <v>-4.453065563253046</v>
+        <v>-4.378593677006565</v>
       </c>
       <c r="G98">
-        <v>-2.397008269468715</v>
+        <v>-1.473319716374504</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.472199789903665</v>
       </c>
       <c r="E99">
-        <v>-44.68499558430932</v>
+        <v>-44.91643683389334</v>
       </c>
       <c r="F99">
-        <v>-5.223437307447753</v>
+        <v>-4.487929062134669</v>
       </c>
       <c r="G99">
-        <v>-1.855366603243017</v>
+        <v>-1.072505346843863</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.8865154092180092</v>
       </c>
       <c r="E100">
-        <v>-45.82120103401883</v>
+        <v>-46.22091584925387</v>
       </c>
       <c r="F100">
-        <v>-4.929510187014613</v>
+        <v>-5.230417959551144</v>
       </c>
       <c r="G100">
-        <v>-3.474686848322126</v>
+        <v>-1.492401700862864</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.3609012867429836</v>
       </c>
       <c r="E101">
-        <v>-49.79139344483857</v>
+        <v>-49.0257428341102</v>
       </c>
       <c r="F101">
-        <v>-4.653850224548007</v>
+        <v>-5.101274653087299</v>
       </c>
       <c r="G101">
-        <v>-3.639244135442679</v>
+        <v>-2.494540251601184</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.1501424285863354</v>
       </c>
       <c r="E102">
-        <v>-52.32517880703231</v>
+        <v>-50.67855886285176</v>
       </c>
       <c r="F102">
-        <v>-5.281171201953267</v>
+        <v>-4.949595611430293</v>
       </c>
       <c r="G102">
-        <v>-4.29660923153914</v>
+        <v>-3.109864729894441</v>
       </c>
     </row>
   </sheetData>
